--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.687617290783407</v>
+        <v>1.249237809752304</v>
       </c>
       <c r="D2" t="n">
-        <v>8.16723990278842</v>
+        <v>1.327176484203118</v>
       </c>
       <c r="E2" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F2" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.855132200881833</v>
+        <v>1.113958982643298</v>
       </c>
       <c r="D3" t="n">
-        <v>12.41731322298977</v>
+        <v>2.017813398735838</v>
       </c>
       <c r="E3" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F3" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.855788543070081</v>
+        <v>1.114065638248888</v>
       </c>
       <c r="D4" t="n">
-        <v>10.39222342092398</v>
+        <v>1.688736305900147</v>
       </c>
       <c r="E4" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F4" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.45875659307134</v>
+        <v>2.837047946374092</v>
       </c>
       <c r="D5" t="n">
-        <v>17.35343367659124</v>
+        <v>2.819932972446077</v>
       </c>
       <c r="E5" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F5" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.49387701230056</v>
+        <v>3.167755014498841</v>
       </c>
       <c r="D6" t="n">
-        <v>18.35755975068582</v>
+        <v>2.983103459486446</v>
       </c>
       <c r="E6" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F6" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.13970571676853</v>
+        <v>2.947702178974887</v>
       </c>
       <c r="D7" t="n">
-        <v>6.726812023536855</v>
+        <v>1.093106953824739</v>
       </c>
       <c r="E7" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F7" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.51036782480235</v>
+        <v>3.170434771530383</v>
       </c>
       <c r="D8" t="n">
-        <v>19.73678357704455</v>
+        <v>3.20722733126974</v>
       </c>
       <c r="E8" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F8" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.72705460748569</v>
+        <v>3.693146373716425</v>
       </c>
       <c r="D9" t="n">
-        <v>23.11729138702362</v>
+        <v>3.756559850391338</v>
       </c>
       <c r="E9" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F9" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.84936808570338</v>
+        <v>4.363022313926798</v>
       </c>
       <c r="D10" t="n">
-        <v>26.02324771155098</v>
+        <v>4.228777753127035</v>
       </c>
       <c r="E10" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F10" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.85932195845408</v>
+        <v>3.227139818248788</v>
       </c>
       <c r="D11" t="n">
-        <v>19.64855626275546</v>
+        <v>3.192890392697762</v>
       </c>
       <c r="E11" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F11" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.09588762198346</v>
+        <v>3.590581738572312</v>
       </c>
       <c r="D12" t="n">
-        <v>12.33930294450952</v>
+        <v>2.005136728482797</v>
       </c>
       <c r="E12" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F12" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.78669074037939</v>
+        <v>1.590337245311651</v>
       </c>
       <c r="D13" t="n">
-        <v>6.800735254367722</v>
+        <v>1.105119478834755</v>
       </c>
       <c r="E13" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F13" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.22104291001898</v>
+        <v>2.635919472878085</v>
       </c>
       <c r="D14" t="n">
-        <v>15.93369773865224</v>
+        <v>2.58922588253099</v>
       </c>
       <c r="E14" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F14" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23.48501490418594</v>
+        <v>3.816314921930215</v>
       </c>
       <c r="D15" t="n">
-        <v>14.10010663189564</v>
+        <v>2.291267327683042</v>
       </c>
       <c r="E15" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F15" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.63816784073518</v>
+        <v>5.303702274119467</v>
       </c>
       <c r="D16" t="n">
-        <v>26.0768096208106</v>
+        <v>4.237481563381722</v>
       </c>
       <c r="E16" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F16" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8.139410298049853</v>
+        <v>1.322654173433101</v>
       </c>
       <c r="D17" t="n">
-        <v>9.062071026848967</v>
+        <v>1.472586541862957</v>
       </c>
       <c r="E17" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F17" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>37.32071954729921</v>
+        <v>6.064616926436121</v>
       </c>
       <c r="D18" t="n">
-        <v>11.52013421587806</v>
+        <v>1.872021810080186</v>
       </c>
       <c r="E18" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F18" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>4.0625</v>
       </c>
       <c r="D19" t="n">
-        <v>24.97682364775292</v>
+        <v>4.05873384275985</v>
       </c>
       <c r="E19" t="n">
-        <v>8.500079649314753</v>
+        <v>1.381262943013647</v>
       </c>
       <c r="F19" t="n">
-        <v>6.358953330697225</v>
+        <v>1.033329916238299</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
